--- a/outputs/calibration_slope.xlsx
+++ b/outputs/calibration_slope.xlsx
@@ -573,7 +573,7 @@
         <v>1.161899391297614</v>
       </c>
       <c r="R3" t="n">
-        <v>1.169608343305597</v>
+        <v>1.169608343305598</v>
       </c>
     </row>
     <row r="4">
@@ -631,7 +631,7 @@
         <v>1.002792231456683</v>
       </c>
       <c r="R4" t="n">
-        <v>1.009211961548081</v>
+        <v>1.00921196154791</v>
       </c>
     </row>
     <row r="5">
@@ -747,7 +747,7 @@
         <v>0.1960114549537242</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1950163581777848</v>
+        <v>0.1950163581777844</v>
       </c>
     </row>
     <row r="7">
@@ -805,7 +805,7 @@
         <v>0.1591071598409313</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1603963817575167</v>
+        <v>0.1603963817576872</v>
       </c>
     </row>
     <row r="9">
@@ -962,7 +962,7 @@
         <v>0.9879079618251688</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9941737594137536</v>
+        <v>0.994173759413754</v>
       </c>
     </row>
     <row r="12">
@@ -1020,7 +1020,7 @@
         <v>0.8807431737638025</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8858809229168216</v>
+        <v>0.885880922916823</v>
       </c>
     </row>
     <row r="13">
@@ -1136,7 +1136,7 @@
         <v>0.1389684471184481</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1404478689263005</v>
+        <v>0.1404478689263001</v>
       </c>
     </row>
     <row r="15">
@@ -1194,7 +1194,7 @@
         <v>0.1071647880613663</v>
       </c>
       <c r="R15" t="n">
-        <v>0.108292836496932</v>
+        <v>0.108292836496931</v>
       </c>
     </row>
     <row r="17">
@@ -1351,7 +1351,7 @@
         <v>0.9597689151244844</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9618379918303672</v>
+        <v>0.9618379918305214</v>
       </c>
     </row>
     <row r="20">
@@ -1409,7 +1409,7 @@
         <v>0.8368606147525948</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8396810930695412</v>
+        <v>0.8396810930695413</v>
       </c>
     </row>
     <row r="21">
@@ -1467,7 +1467,7 @@
         <v>1.101724598818951</v>
       </c>
       <c r="R21" t="n">
-        <v>1.104227880263001</v>
+        <v>1.104227880262997</v>
       </c>
     </row>
     <row r="22">
@@ -1525,7 +1525,7 @@
         <v>0.1419556836944667</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1423898884326342</v>
+        <v>0.1423898884324754</v>
       </c>
     </row>
     <row r="23">
@@ -1583,7 +1583,7 @@
         <v>0.1229083003718896</v>
       </c>
       <c r="R23" t="n">
-        <v>0.122156898760826</v>
+        <v>0.1221568987609801</v>
       </c>
     </row>
     <row r="25">
@@ -1798,7 +1798,7 @@
         <v>0.9886857811481652</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9880111510067382</v>
+        <v>0.9880111510067384</v>
       </c>
     </row>
     <row r="29">
@@ -1856,7 +1856,7 @@
         <v>1.286492074928852</v>
       </c>
       <c r="R29" t="n">
-        <v>1.284603919875827</v>
+        <v>1.284603919875825</v>
       </c>
     </row>
     <row r="30">
@@ -1914,7 +1914,7 @@
         <v>0.1621340944643261</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1612734299106735</v>
+        <v>0.1612734299106711</v>
       </c>
     </row>
     <row r="31">
@@ -1972,7 +1972,7 @@
         <v>0.1356721993163607</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1353193389584157</v>
+        <v>0.1353193389584151</v>
       </c>
     </row>
     <row r="33">
@@ -2129,7 +2129,7 @@
         <v>0.9780912565762784</v>
       </c>
       <c r="R35" t="n">
-        <v>0.9821573422096812</v>
+        <v>0.9821573422096814</v>
       </c>
     </row>
     <row r="36">
@@ -2187,7 +2187,7 @@
         <v>0.8177093486665258</v>
       </c>
       <c r="R36" t="n">
-        <v>0.8200479338961787</v>
+        <v>0.8200479338961922</v>
       </c>
     </row>
     <row r="37">
@@ -2245,7 +2245,7 @@
         <v>1.155930083382957</v>
       </c>
       <c r="R37" t="n">
-        <v>1.159572643040802</v>
+        <v>1.159572643040801</v>
       </c>
     </row>
     <row r="38">
@@ -2303,7 +2303,7 @@
         <v>0.1778388268066787</v>
       </c>
       <c r="R38" t="n">
-        <v>0.1774153008311203</v>
+        <v>0.1774153008311197</v>
       </c>
     </row>
     <row r="39">
@@ -2361,7 +2361,7 @@
         <v>0.1603819079097526</v>
       </c>
       <c r="R39" t="n">
-        <v>0.1621094083135025</v>
+        <v>0.1621094083134892</v>
       </c>
     </row>
     <row r="41">
@@ -2518,7 +2518,7 @@
         <v>0.8533860356566768</v>
       </c>
       <c r="R43" t="n">
-        <v>0.8542248153973885</v>
+        <v>0.8542248153973886</v>
       </c>
     </row>
     <row r="44">
@@ -2692,7 +2692,7 @@
         <v>0.1693148239466468</v>
       </c>
       <c r="R46" t="n">
-        <v>0.1688701017040283</v>
+        <v>0.1688701017040282</v>
       </c>
     </row>
     <row r="47">
@@ -2750,7 +2750,7 @@
         <v>0.1400797985589866</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1422740924270096</v>
+        <v>0.1422740924270097</v>
       </c>
     </row>
     <row r="49">
@@ -2965,7 +2965,7 @@
         <v>0.8225539649092988</v>
       </c>
       <c r="R52" t="n">
-        <v>0.8227471561248585</v>
+        <v>0.8227471561248595</v>
       </c>
     </row>
     <row r="53">
@@ -3139,7 +3139,7 @@
         <v>0.1147876838245621</v>
       </c>
       <c r="R55" t="n">
-        <v>0.1156234481521711</v>
+        <v>0.1156234481521701</v>
       </c>
     </row>
     <row r="57">
@@ -3296,7 +3296,7 @@
         <v>1.057723829946059</v>
       </c>
       <c r="R59" t="n">
-        <v>1.062970870817025</v>
+        <v>1.062970870817017</v>
       </c>
     </row>
     <row r="60">
@@ -3354,7 +3354,7 @@
         <v>0.9146797735316852</v>
       </c>
       <c r="R60" t="n">
-        <v>0.9188879216057124</v>
+        <v>0.918887921605712</v>
       </c>
     </row>
     <row r="61">
@@ -3412,7 +3412,7 @@
         <v>1.208902079669952</v>
       </c>
       <c r="R61" t="n">
-        <v>1.21525915735447</v>
+        <v>1.215259157354471</v>
       </c>
     </row>
     <row r="62">
@@ -3470,7 +3470,7 @@
         <v>0.1511782497238934</v>
       </c>
       <c r="R62" t="n">
-        <v>0.1522882865374453</v>
+        <v>0.152288286537454</v>
       </c>
     </row>
     <row r="63">
@@ -3528,7 +3528,7 @@
         <v>0.1430440564143738</v>
       </c>
       <c r="R63" t="n">
-        <v>0.1440829492113127</v>
+        <v>0.1440829492113049</v>
       </c>
     </row>
     <row r="65">
@@ -3801,7 +3801,7 @@
         <v>1.189254616198394</v>
       </c>
       <c r="R69" t="n">
-        <v>1.197540153935455</v>
+        <v>1.197540153935456</v>
       </c>
     </row>
     <row r="70">
@@ -3859,7 +3859,7 @@
         <v>0.1295993349731457</v>
       </c>
       <c r="R70" t="n">
-        <v>0.1303194821969367</v>
+        <v>0.1303194821969373</v>
       </c>
     </row>
     <row r="71">
@@ -4074,7 +4074,7 @@
         <v>0.8657843133230879</v>
       </c>
       <c r="R75" t="n">
-        <v>0.8632963134304273</v>
+        <v>0.8632963134304275</v>
       </c>
     </row>
     <row r="76">
@@ -4132,7 +4132,7 @@
         <v>0.7288177472368562</v>
       </c>
       <c r="R76" t="n">
-        <v>0.7267900378494907</v>
+        <v>0.7267900378494837</v>
       </c>
     </row>
     <row r="77">
@@ -4248,7 +4248,7 @@
         <v>0.1783764958164585</v>
       </c>
       <c r="R78" t="n">
-        <v>0.1787470748745187</v>
+        <v>0.1787470748745188</v>
       </c>
     </row>
     <row r="79">
@@ -4306,7 +4306,7 @@
         <v>0.1369665660862317</v>
       </c>
       <c r="R79" t="n">
-        <v>0.1365062755809366</v>
+        <v>0.1365062755809437</v>
       </c>
     </row>
     <row r="81">
@@ -4521,7 +4521,7 @@
         <v>0.895209608607335</v>
       </c>
       <c r="R84" t="n">
-        <v>0.9019026748384432</v>
+        <v>0.9019026748384458</v>
       </c>
     </row>
     <row r="85">
@@ -4695,7 +4695,7 @@
         <v>0.1118878949869541</v>
       </c>
       <c r="R87" t="n">
-        <v>0.1132580123696191</v>
+        <v>0.1132580123696165</v>
       </c>
     </row>
     <row r="89">
@@ -4852,7 +4852,7 @@
         <v>0.982231003420204</v>
       </c>
       <c r="R91" t="n">
-        <v>0.9877174546110874</v>
+        <v>0.9877174546110872</v>
       </c>
     </row>
     <row r="92">
@@ -4910,7 +4910,7 @@
         <v>0.8876830972796648</v>
       </c>
       <c r="R92" t="n">
-        <v>0.8905733027279478</v>
+        <v>0.890573302727948</v>
       </c>
     </row>
     <row r="93">
@@ -5026,7 +5026,7 @@
         <v>0.1080968504075512</v>
       </c>
       <c r="R94" t="n">
-        <v>0.1079810153276899</v>
+        <v>0.1079810153276901</v>
       </c>
     </row>
     <row r="95">
@@ -5084,7 +5084,7 @@
         <v>0.09454790614053921</v>
       </c>
       <c r="R95" t="n">
-        <v>0.09714415188313963</v>
+        <v>0.09714415188313918</v>
       </c>
     </row>
     <row r="97">
@@ -5241,7 +5241,7 @@
         <v>1.113538568316086</v>
       </c>
       <c r="R99" t="n">
-        <v>1.121237046646195</v>
+        <v>1.121237046646212</v>
       </c>
     </row>
     <row r="100">
@@ -5299,7 +5299,7 @@
         <v>0.9657549440984168</v>
       </c>
       <c r="R100" t="n">
-        <v>0.973264072005994</v>
+        <v>0.9732640720059944</v>
       </c>
     </row>
     <row r="101">
@@ -5415,7 +5415,7 @@
         <v>0.1739322441538216</v>
       </c>
       <c r="R102" t="n">
-        <v>0.1746045758646508</v>
+        <v>0.1746045758646335</v>
       </c>
     </row>
     <row r="103">
@@ -5473,7 +5473,7 @@
         <v>0.1477836242176693</v>
       </c>
       <c r="R103" t="n">
-        <v>0.1479729746402008</v>
+        <v>0.1479729746402176</v>
       </c>
     </row>
     <row r="105">
@@ -5688,7 +5688,7 @@
         <v>0.8534786727539643</v>
       </c>
       <c r="R108" t="n">
-        <v>0.8579889539395228</v>
+        <v>0.8579889539396387</v>
       </c>
     </row>
     <row r="109">
@@ -5862,7 +5862,7 @@
         <v>0.1077065669862601</v>
       </c>
       <c r="R111" t="n">
-        <v>0.1085019162062872</v>
+        <v>0.1085019162061713</v>
       </c>
     </row>
     <row r="113">
@@ -6019,7 +6019,7 @@
         <v>0.9838480605607024</v>
       </c>
       <c r="R115" t="n">
-        <v>0.9904924857466664</v>
+        <v>0.9904924857463552</v>
       </c>
     </row>
     <row r="116">
@@ -6077,7 +6077,7 @@
         <v>0.8399839172810983</v>
       </c>
       <c r="R116" t="n">
-        <v>0.8453941139913576</v>
+        <v>0.8453941139913573</v>
       </c>
     </row>
     <row r="117">
@@ -6135,7 +6135,7 @@
         <v>1.141156164522896</v>
       </c>
       <c r="R117" t="n">
-        <v>1.149820819986031</v>
+        <v>1.149820819986029</v>
       </c>
     </row>
     <row r="118">
@@ -6193,7 +6193,7 @@
         <v>0.1573081039621936</v>
       </c>
       <c r="R118" t="n">
-        <v>0.159328334239365</v>
+        <v>0.1593283342396742</v>
       </c>
     </row>
     <row r="119">
@@ -6251,7 +6251,7 @@
         <v>0.1438641432796041</v>
       </c>
       <c r="R119" t="n">
-        <v>0.1450983717553088</v>
+        <v>0.1450983717549978</v>
       </c>
     </row>
     <row r="121">
@@ -6408,7 +6408,7 @@
         <v>0.847904112617511</v>
       </c>
       <c r="R123" t="n">
-        <v>0.8535581245002377</v>
+        <v>0.8535581245002378</v>
       </c>
     </row>
     <row r="124">
@@ -6466,7 +6466,7 @@
         <v>0.6738754695273115</v>
       </c>
       <c r="R124" t="n">
-        <v>0.6795193595721035</v>
+        <v>0.6795193595721036</v>
       </c>
     </row>
     <row r="125">
@@ -6582,7 +6582,7 @@
         <v>0.2106646657137731</v>
       </c>
       <c r="R126" t="n">
-        <v>0.2136811944972998</v>
+        <v>0.2136811944972997</v>
       </c>
     </row>
     <row r="127">
@@ -6869,7 +6869,7 @@
         <v>1.002903376277437</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9553631489664034</v>
+        <v>0.955363148966313</v>
       </c>
     </row>
     <row r="5">
@@ -6927,7 +6927,7 @@
         <v>1.358510068075325</v>
       </c>
       <c r="R5" t="n">
-        <v>1.299019728663613</v>
+        <v>1.299019728663381</v>
       </c>
     </row>
     <row r="6">
@@ -6985,7 +6985,7 @@
         <v>0.1961457329518421</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1886388508089278</v>
+        <v>0.1886388508086956</v>
       </c>
     </row>
     <row r="7">
@@ -7043,7 +7043,7 @@
         <v>0.1594609588460454</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1550177288882819</v>
+        <v>0.1550177288883723</v>
       </c>
     </row>
     <row r="9">
@@ -7200,7 +7200,7 @@
         <v>0.9887945347230191</v>
       </c>
       <c r="R11" t="n">
-        <v>0.934748809751862</v>
+        <v>0.934748809751878</v>
       </c>
     </row>
     <row r="12">
@@ -7258,7 +7258,7 @@
         <v>0.8815816371377793</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8357563556729077</v>
+        <v>0.8357563556729071</v>
       </c>
     </row>
     <row r="13">
@@ -7374,7 +7374,7 @@
         <v>0.1392116992751573</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1301386476737157</v>
+        <v>0.1301386476737</v>
       </c>
     </row>
     <row r="15">
@@ -7432,7 +7432,7 @@
         <v>0.1072128975852399</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0989924540789543</v>
+        <v>0.09899245407897095</v>
       </c>
     </row>
     <row r="17">
@@ -7647,7 +7647,7 @@
         <v>0.837673951374271</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8020398787157194</v>
+        <v>0.8020398787157266</v>
       </c>
     </row>
     <row r="21">
@@ -7821,7 +7821,7 @@
         <v>0.1230449455089254</v>
       </c>
       <c r="R23" t="n">
-        <v>0.116059800291477</v>
+        <v>0.1160598002914698</v>
       </c>
     </row>
     <row r="25">
@@ -7978,7 +7978,7 @@
         <v>1.125158982022397</v>
       </c>
       <c r="R27" t="n">
-        <v>1.126042613648649</v>
+        <v>1.12604261364865</v>
       </c>
     </row>
     <row r="28">
@@ -8036,7 +8036,7 @@
         <v>0.9892858224738204</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9862177706892664</v>
+        <v>0.986217770689246</v>
       </c>
     </row>
     <row r="29">
@@ -8094,7 +8094,7 @@
         <v>1.287285681115718</v>
       </c>
       <c r="R29" t="n">
-        <v>1.287676742016492</v>
+        <v>1.287676742016519</v>
       </c>
     </row>
     <row r="30">
@@ -8152,7 +8152,7 @@
         <v>0.1621266990933214</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1616341283678433</v>
+        <v>0.1616341283678684</v>
       </c>
     </row>
     <row r="31">
@@ -8210,7 +8210,7 @@
         <v>0.1358731595485763</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1398248429593826</v>
+        <v>0.1398248429594043</v>
       </c>
     </row>
     <row r="33">
@@ -8367,7 +8367,7 @@
         <v>0.9792164786551976</v>
       </c>
       <c r="R35" t="n">
-        <v>0.928096807323717</v>
+        <v>0.9280968073238982</v>
       </c>
     </row>
     <row r="36">
@@ -8425,7 +8425,7 @@
         <v>0.8185413239730829</v>
       </c>
       <c r="R36" t="n">
-        <v>0.7771568325257607</v>
+        <v>0.7771568325257604</v>
       </c>
     </row>
     <row r="37">
@@ -8541,7 +8541,7 @@
         <v>0.1780306610876596</v>
       </c>
       <c r="R38" t="n">
-        <v>0.1664420683880306</v>
+        <v>0.1664420683878496</v>
       </c>
     </row>
     <row r="39">
@@ -8599,7 +8599,7 @@
         <v>0.1606751546821147</v>
       </c>
       <c r="R39" t="n">
-        <v>0.1509399747979563</v>
+        <v>0.1509399747981378</v>
       </c>
     </row>
     <row r="41">
@@ -8814,7 +8814,7 @@
         <v>0.7139669681278994</v>
       </c>
       <c r="R44" t="n">
-        <v>0.6717526094061892</v>
+        <v>0.6717526094062023</v>
       </c>
     </row>
     <row r="45">
@@ -8872,7 +8872,7 @@
         <v>1.023451270987977</v>
       </c>
       <c r="R45" t="n">
-        <v>0.959050655366612</v>
+        <v>0.9590506553668074</v>
       </c>
     </row>
     <row r="46">
@@ -8930,7 +8930,7 @@
         <v>0.1693181933588122</v>
       </c>
       <c r="R46" t="n">
-        <v>0.1556963507766774</v>
+        <v>0.1556963507768728</v>
       </c>
     </row>
     <row r="47">
@@ -8988,7 +8988,7 @@
         <v>0.1401661095012655</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1316016951837454</v>
+        <v>0.1316016951837323</v>
       </c>
     </row>
     <row r="49">
@@ -9145,7 +9145,7 @@
         <v>0.9382951100513548</v>
       </c>
       <c r="R51" t="n">
-        <v>0.9004777029018346</v>
+        <v>0.9004777029018347</v>
       </c>
     </row>
     <row r="52">
@@ -9203,7 +9203,7 @@
         <v>0.8232671897377</v>
       </c>
       <c r="R52" t="n">
-        <v>0.7917992748356693</v>
+        <v>0.7917992748356697</v>
       </c>
     </row>
     <row r="53">
@@ -9261,7 +9261,7 @@
         <v>1.076186864773203</v>
       </c>
       <c r="R53" t="n">
-        <v>1.031275935105137</v>
+        <v>1.031275935105128</v>
       </c>
     </row>
     <row r="54">
@@ -9319,7 +9319,7 @@
         <v>0.1378917547218481</v>
       </c>
       <c r="R54" t="n">
-        <v>0.130798232203302</v>
+        <v>0.1307982322032932</v>
       </c>
     </row>
     <row r="55">
@@ -9377,7 +9377,7 @@
         <v>0.1150279203136548</v>
       </c>
       <c r="R55" t="n">
-        <v>0.1086784280661653</v>
+        <v>0.108678428066165</v>
       </c>
     </row>
     <row r="57">
@@ -9534,7 +9534,7 @@
         <v>1.058745064258455</v>
       </c>
       <c r="R59" t="n">
-        <v>1.02675137385498</v>
+        <v>1.026751373854973</v>
       </c>
     </row>
     <row r="60">
@@ -9592,7 +9592,7 @@
         <v>0.9155106209053636</v>
       </c>
       <c r="R60" t="n">
-        <v>0.8901170227598072</v>
+        <v>0.8901170227598071</v>
       </c>
     </row>
     <row r="61">
@@ -9650,7 +9650,7 @@
         <v>1.209926143215579</v>
       </c>
       <c r="R61" t="n">
-        <v>1.174743438396776</v>
+        <v>1.174743438396995</v>
       </c>
     </row>
     <row r="62">
@@ -9708,7 +9708,7 @@
         <v>0.1511810789571242</v>
       </c>
       <c r="R62" t="n">
-        <v>0.1479920645417965</v>
+        <v>0.1479920645420219</v>
       </c>
     </row>
     <row r="63">
@@ -9766,7 +9766,7 @@
         <v>0.143234443353091</v>
       </c>
       <c r="R63" t="n">
-        <v>0.1366343510951726</v>
+        <v>0.1366343510951659</v>
       </c>
     </row>
     <row r="65">
@@ -9923,7 +9923,7 @@
         <v>1.06081188120445</v>
       </c>
       <c r="R67" t="n">
-        <v>0.9939258488230118</v>
+        <v>0.9939258488230061</v>
       </c>
     </row>
     <row r="68">
@@ -9981,7 +9981,7 @@
         <v>0.9389315647553912</v>
       </c>
       <c r="R68" t="n">
-        <v>0.8763846821547869</v>
+        <v>0.8763846821549927</v>
       </c>
     </row>
     <row r="69">
@@ -10097,7 +10097,7 @@
         <v>0.1296718746609058</v>
       </c>
       <c r="R70" t="n">
-        <v>0.1227298325022443</v>
+        <v>0.1227298325022494</v>
       </c>
     </row>
     <row r="71">
@@ -10155,7 +10155,7 @@
         <v>0.1218803164490586</v>
       </c>
       <c r="R71" t="n">
-        <v>0.1175411666682249</v>
+        <v>0.1175411666680134</v>
       </c>
     </row>
     <row r="73">
@@ -10312,7 +10312,7 @@
         <v>0.8666449161375227</v>
       </c>
       <c r="R75" t="n">
-        <v>0.8067495487413562</v>
+        <v>0.8067495487413744</v>
       </c>
     </row>
     <row r="76">
@@ -10428,7 +10428,7 @@
         <v>1.045527008524342</v>
       </c>
       <c r="R77" t="n">
-        <v>0.9741321477347246</v>
+        <v>0.9741321477332838</v>
       </c>
     </row>
     <row r="78">
@@ -10486,7 +10486,7 @@
         <v>0.1788820923868188</v>
       </c>
       <c r="R78" t="n">
-        <v>0.1673825989933684</v>
+        <v>0.1673825989919094</v>
       </c>
     </row>
     <row r="79">
@@ -10544,7 +10544,7 @@
         <v>0.1371062207709555</v>
       </c>
       <c r="R79" t="n">
-        <v>0.1257265336013337</v>
+        <v>0.1257265336013519</v>
       </c>
     </row>
     <row r="81">
@@ -10701,7 +10701,7 @@
         <v>1.008052063486204</v>
       </c>
       <c r="R83" t="n">
-        <v>0.9455955744251522</v>
+        <v>0.9455955744251532</v>
       </c>
     </row>
     <row r="84">
@@ -10759,7 +10759,7 @@
         <v>0.8959870003769894</v>
       </c>
       <c r="R84" t="n">
-        <v>0.8414517859723361</v>
+        <v>0.8414517859723069</v>
       </c>
     </row>
     <row r="85">
@@ -10875,7 +10875,7 @@
         <v>0.1411332312766189</v>
       </c>
       <c r="R86" t="n">
-        <v>0.1332399106746965</v>
+        <v>0.1332399106746955</v>
       </c>
     </row>
     <row r="87">
@@ -10933,7 +10933,7 @@
         <v>0.1120650631092146</v>
       </c>
       <c r="R87" t="n">
-        <v>0.1041437884528161</v>
+        <v>0.1041437884528463</v>
       </c>
     </row>
     <row r="89">
@@ -11206,7 +11206,7 @@
         <v>1.091204291804005</v>
       </c>
       <c r="R93" t="n">
-        <v>1.094139954912389</v>
+        <v>1.094139954912388</v>
       </c>
     </row>
     <row r="94">
@@ -11264,7 +11264,7 @@
         <v>0.1083135583956057</v>
       </c>
       <c r="R94" t="n">
-        <v>0.1093790978942765</v>
+        <v>0.109379097894276</v>
       </c>
     </row>
     <row r="95">
@@ -11479,7 +11479,7 @@
         <v>1.114407351066702</v>
       </c>
       <c r="R99" t="n">
-        <v>1.061078280550113</v>
+        <v>1.061078280550095</v>
       </c>
     </row>
     <row r="100">
@@ -11537,7 +11537,7 @@
         <v>0.9665535040765914</v>
       </c>
       <c r="R100" t="n">
-        <v>0.9163415878537148</v>
+        <v>0.9163415878537144</v>
       </c>
     </row>
     <row r="101">
@@ -11595,7 +11595,7 @@
         <v>1.288403965060471</v>
       </c>
       <c r="R101" t="n">
-        <v>1.227029251367013</v>
+        <v>1.227029251367032</v>
       </c>
     </row>
     <row r="102">
@@ -11653,7 +11653,7 @@
         <v>0.1739966139937688</v>
       </c>
       <c r="R102" t="n">
-        <v>0.1659509708169</v>
+        <v>0.1659509708169367</v>
       </c>
     </row>
     <row r="103">
@@ -11711,7 +11711,7 @@
         <v>0.1478538469901107</v>
       </c>
       <c r="R103" t="n">
-        <v>0.1447366926963983</v>
+        <v>0.1447366926963805</v>
       </c>
     </row>
     <row r="105">
@@ -11868,7 +11868,7 @@
         <v>0.962020097293964</v>
       </c>
       <c r="R107" t="n">
-        <v>0.9367178089542674</v>
+        <v>0.9367178089542672</v>
       </c>
     </row>
     <row r="108">
@@ -11926,7 +11926,7 @@
         <v>0.8540046173832229</v>
       </c>
       <c r="R108" t="n">
-        <v>0.8280499139919915</v>
+        <v>0.8280499139919913</v>
       </c>
     </row>
     <row r="109">
@@ -11984,7 +11984,7 @@
         <v>1.080987839249163</v>
       </c>
       <c r="R109" t="n">
-        <v>1.051235791182313</v>
+        <v>1.051235791182947</v>
       </c>
     </row>
     <row r="110">
@@ -12042,7 +12042,7 @@
         <v>0.1189677419551988</v>
       </c>
       <c r="R110" t="n">
-        <v>0.1145179822280453</v>
+        <v>0.1145179822286801</v>
       </c>
     </row>
     <row r="111">
@@ -12100,7 +12100,7 @@
         <v>0.1080154799107411</v>
       </c>
       <c r="R111" t="n">
-        <v>0.1086678949622759</v>
+        <v>0.1086678949622758</v>
       </c>
     </row>
     <row r="113">
@@ -12257,7 +12257,7 @@
         <v>0.9849355002834392</v>
       </c>
       <c r="R115" t="n">
-        <v>0.9166232592516944</v>
+        <v>0.9166232592516946</v>
       </c>
     </row>
     <row r="116">
@@ -12315,7 +12315,7 @@
         <v>0.841051873086784</v>
       </c>
       <c r="R116" t="n">
-        <v>0.7845588362727107</v>
+        <v>0.7845588362727324</v>
       </c>
     </row>
     <row r="117">
@@ -12373,7 +12373,7 @@
         <v>1.142522402705946</v>
       </c>
       <c r="R117" t="n">
-        <v>1.066151490720828</v>
+        <v>1.06615149072002</v>
       </c>
     </row>
     <row r="118">
@@ -12431,7 +12431,7 @@
         <v>0.1575869024225072</v>
       </c>
       <c r="R118" t="n">
-        <v>0.1495282314691341</v>
+        <v>0.1495282314683258</v>
       </c>
     </row>
     <row r="119">
@@ -12489,7 +12489,7 @@
         <v>0.1438836271966553</v>
       </c>
       <c r="R119" t="n">
-        <v>0.1320644229789837</v>
+        <v>0.1320644229789623</v>
       </c>
     </row>
     <row r="121">
@@ -12646,7 +12646,7 @@
         <v>0.8483321728011987</v>
       </c>
       <c r="R123" t="n">
-        <v>0.8351840264898912</v>
+        <v>0.835184026489891</v>
       </c>
     </row>
     <row r="124">
@@ -12704,7 +12704,7 @@
         <v>0.6741381226263126</v>
       </c>
       <c r="R124" t="n">
-        <v>0.6614909872276351</v>
+        <v>0.6614909872276352</v>
       </c>
     </row>
     <row r="125">
@@ -12762,7 +12762,7 @@
         <v>1.058870737568721</v>
       </c>
       <c r="R125" t="n">
-        <v>1.043309508558138</v>
+        <v>1.043309508558683</v>
       </c>
     </row>
     <row r="126">
@@ -12820,7 +12820,7 @@
         <v>0.2105385647675221</v>
       </c>
       <c r="R126" t="n">
-        <v>0.2081254820682464</v>
+        <v>0.2081254820687922</v>
       </c>
     </row>
     <row r="127">
@@ -12878,7 +12878,7 @@
         <v>0.1741940501748861</v>
       </c>
       <c r="R127" t="n">
-        <v>0.1736930392622561</v>
+        <v>0.1736930392622558</v>
       </c>
     </row>
   </sheetData>
@@ -13107,7 +13107,7 @@
         <v>1.002792545642779</v>
       </c>
       <c r="R4" t="n">
-        <v>1.009217418600648</v>
+        <v>1.009217418600477</v>
       </c>
     </row>
     <row r="5">
@@ -13223,7 +13223,7 @@
         <v>0.1960115315637836</v>
       </c>
       <c r="R6" t="n">
-        <v>0.195016980159602</v>
+        <v>0.1950169801596018</v>
       </c>
     </row>
     <row r="7">
@@ -13281,7 +13281,7 @@
         <v>0.1591072353119549</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1603968764674308</v>
+        <v>0.1603968764676009</v>
       </c>
     </row>
     <row r="9">
@@ -13438,7 +13438,7 @@
         <v>0.9879083318550984</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9941793961309834</v>
+        <v>0.9941793961309832</v>
       </c>
     </row>
     <row r="12">
@@ -13496,7 +13496,7 @@
         <v>0.8807435290905181</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8858863571595701</v>
+        <v>0.8858863571595715</v>
       </c>
     </row>
     <row r="13">
@@ -13670,7 +13670,7 @@
         <v>0.1071648027645803</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1082930389714133</v>
+        <v>0.1082930389714116</v>
       </c>
     </row>
     <row r="17">
@@ -13827,7 +13827,7 @@
         <v>0.9597692537789472</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9618432386839904</v>
+        <v>0.961843238684145</v>
       </c>
     </row>
     <row r="20">
@@ -13885,7 +13885,7 @@
         <v>0.8368609024700935</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8396849852104205</v>
+        <v>0.8396849852104206</v>
       </c>
     </row>
     <row r="21">
@@ -13943,7 +13943,7 @@
         <v>1.101724959779673</v>
       </c>
       <c r="R21" t="n">
-        <v>1.104233352516694</v>
+        <v>1.104233352516689</v>
       </c>
     </row>
     <row r="22">
@@ -14001,7 +14001,7 @@
         <v>0.1419557060007258</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1423901138327037</v>
+        <v>0.1423901138325444</v>
       </c>
     </row>
     <row r="23">
@@ -14059,7 +14059,7 @@
         <v>0.1229083513088537</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1221582534735699</v>
+        <v>0.1221582534737244</v>
       </c>
     </row>
     <row r="25">
@@ -14274,7 +14274,7 @@
         <v>0.9886861659210232</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9880167635132772</v>
+        <v>0.9880167635132774</v>
       </c>
     </row>
     <row r="29">
@@ -14332,7 +14332,7 @@
         <v>1.286492582678794</v>
       </c>
       <c r="R29" t="n">
-        <v>1.284612838760336</v>
+        <v>1.284612838760333</v>
       </c>
     </row>
     <row r="30">
@@ -14390,7 +14390,7 @@
         <v>0.1621341444195803</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1612753025114424</v>
+        <v>0.1612753025114397</v>
       </c>
     </row>
     <row r="31">
@@ -14448,7 +14448,7 @@
         <v>0.1356722723381906</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1353207727356168</v>
+        <v>0.1353207727356164</v>
       </c>
     </row>
     <row r="33">
@@ -14663,7 +14663,7 @@
         <v>0.8177096166077895</v>
       </c>
       <c r="R36" t="n">
-        <v>0.8200520383557327</v>
+        <v>0.8200520383557461</v>
       </c>
     </row>
     <row r="37">
@@ -14837,7 +14837,7 @@
         <v>0.1603819687082361</v>
       </c>
       <c r="R39" t="n">
-        <v>0.1621103356239765</v>
+        <v>0.162110335623963</v>
       </c>
     </row>
     <row r="41">
@@ -14994,7 +14994,7 @@
         <v>0.8533863372025826</v>
       </c>
       <c r="R43" t="n">
-        <v>0.8542295067869831</v>
+        <v>0.8542295067869827</v>
       </c>
     </row>
     <row r="44">
@@ -15110,7 +15110,7 @@
         <v>1.02270120706739</v>
       </c>
       <c r="R45" t="n">
-        <v>1.023100308234477</v>
+        <v>1.023100308234476</v>
       </c>
     </row>
     <row r="46">
@@ -15168,7 +15168,7 @@
         <v>0.1693148698648074</v>
       </c>
       <c r="R46" t="n">
-        <v>0.1688708014474934</v>
+        <v>0.1688708014474933</v>
       </c>
     </row>
     <row r="47">
@@ -15226,7 +15226,7 @@
         <v>0.140079803256719</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1422747073140282</v>
+        <v>0.1422747073140279</v>
       </c>
     </row>
     <row r="49">
@@ -15441,7 +15441,7 @@
         <v>0.8225543150550604</v>
       </c>
       <c r="R52" t="n">
-        <v>0.822752091952196</v>
+        <v>0.8227520919521968</v>
       </c>
     </row>
     <row r="53">
@@ -15615,7 +15615,7 @@
         <v>0.1147877026722505</v>
       </c>
       <c r="R55" t="n">
-        <v>0.1156242552849172</v>
+        <v>0.1156242552849164</v>
       </c>
     </row>
     <row r="57">
@@ -15772,7 +15772,7 @@
         <v>1.057724253867514</v>
       </c>
       <c r="R59" t="n">
-        <v>1.062977392363079</v>
+        <v>1.06297739236307</v>
       </c>
     </row>
     <row r="60">
@@ -15830,7 +15830,7 @@
         <v>0.914680157498837</v>
       </c>
       <c r="R60" t="n">
-        <v>0.9188935220373924</v>
+        <v>0.9188935220373926</v>
       </c>
     </row>
     <row r="61">
@@ -15946,7 +15946,7 @@
         <v>0.151178279926544</v>
       </c>
       <c r="R62" t="n">
-        <v>0.15228881420512</v>
+        <v>0.1522888142051289</v>
       </c>
     </row>
     <row r="63">
@@ -16004,7 +16004,7 @@
         <v>0.1430440963686765</v>
       </c>
       <c r="R63" t="n">
-        <v>0.1440838703256868</v>
+        <v>0.1440838703256777</v>
       </c>
     </row>
     <row r="65">
@@ -16219,7 +16219,7 @@
         <v>0.9378332152243584</v>
       </c>
       <c r="R68" t="n">
-        <v>0.9442325822170654</v>
+        <v>0.9442325822170652</v>
       </c>
     </row>
     <row r="69">
@@ -16335,7 +16335,7 @@
         <v>0.1295994077597835</v>
       </c>
       <c r="R70" t="n">
-        <v>0.1303195373964774</v>
+        <v>0.1303195373964767</v>
       </c>
     </row>
     <row r="71">
@@ -16393,7 +16393,7 @@
         <v>0.1218224514950835</v>
       </c>
       <c r="R71" t="n">
-        <v>0.1229938795054961</v>
+        <v>0.122993879505497</v>
       </c>
     </row>
     <row r="73">
@@ -16608,7 +16608,7 @@
         <v>0.7288180160964881</v>
       </c>
       <c r="R76" t="n">
-        <v>0.7267945680617436</v>
+        <v>0.7267945680617368</v>
       </c>
     </row>
     <row r="77">
@@ -16782,7 +16782,7 @@
         <v>0.1369666212859091</v>
       </c>
       <c r="R79" t="n">
-        <v>0.1365067107240017</v>
+        <v>0.1365067107240084</v>
       </c>
     </row>
     <row r="81">
@@ -16939,7 +16939,7 @@
         <v>1.007097843448748</v>
       </c>
       <c r="R83" t="n">
-        <v>1.015165805900698</v>
+        <v>1.015165805900697</v>
       </c>
     </row>
     <row r="84">
@@ -16997,7 +16997,7 @@
         <v>0.8952099138147199</v>
       </c>
       <c r="R84" t="n">
-        <v>0.9019074730269816</v>
+        <v>0.9019074730269844</v>
       </c>
     </row>
     <row r="85">
@@ -17113,7 +17113,7 @@
         <v>0.1411446566923249</v>
       </c>
       <c r="R86" t="n">
-        <v>0.1414937702648893</v>
+        <v>0.1414937702648895</v>
       </c>
     </row>
     <row r="87">
@@ -17171,7 +17171,7 @@
         <v>0.1118879296340284</v>
       </c>
       <c r="R87" t="n">
-        <v>0.113258332873716</v>
+        <v>0.113258332873713</v>
       </c>
     </row>
     <row r="89">
@@ -17328,7 +17328,7 @@
         <v>0.9822313778405838</v>
       </c>
       <c r="R91" t="n">
-        <v>0.9877230868369686</v>
+        <v>0.9877230868369689</v>
       </c>
     </row>
     <row r="92">
@@ -17502,7 +17502,7 @@
         <v>0.1080968953502066</v>
       </c>
       <c r="R94" t="n">
-        <v>0.1079812043270421</v>
+        <v>0.1079812043270418</v>
       </c>
     </row>
     <row r="95">
@@ -17560,7 +17560,7 @@
         <v>0.09454796307814706</v>
       </c>
       <c r="R95" t="n">
-        <v>0.09714501020839061</v>
+        <v>0.09714501020839084</v>
       </c>
     </row>
     <row r="97">
@@ -17717,7 +17717,7 @@
         <v>1.11353896919583</v>
       </c>
       <c r="R99" t="n">
-        <v>1.12124316243101</v>
+        <v>1.121243162431026</v>
       </c>
     </row>
     <row r="100">
@@ -17775,7 +17775,7 @@
         <v>0.9657552824146044</v>
       </c>
       <c r="R100" t="n">
-        <v>0.9732691582777528</v>
+        <v>0.9732691582777526</v>
       </c>
     </row>
     <row r="101">
@@ -17891,7 +17891,7 @@
         <v>0.1739322796811757</v>
       </c>
       <c r="R102" t="n">
-        <v>0.174605063546416</v>
+        <v>0.1746050635463998</v>
       </c>
     </row>
     <row r="103">
@@ -17949,7 +17949,7 @@
         <v>0.1477836867812258</v>
       </c>
       <c r="R103" t="n">
-        <v>0.1479740041532567</v>
+        <v>0.1479740041532736</v>
       </c>
     </row>
     <row r="105">
@@ -18106,7 +18106,7 @@
         <v>0.9611855928293886</v>
       </c>
       <c r="R107" t="n">
-        <v>0.9664963112775496</v>
+        <v>0.96649631127755</v>
       </c>
     </row>
     <row r="108">
@@ -18164,7 +18164,7 @@
         <v>0.853479017316064</v>
       </c>
       <c r="R108" t="n">
-        <v>0.8579943142511284</v>
+        <v>0.8579943142512442</v>
       </c>
     </row>
     <row r="109">
@@ -18280,7 +18280,7 @@
         <v>0.1187553831958861</v>
       </c>
       <c r="R110" t="n">
-        <v>0.1190550973613765</v>
+        <v>0.1190550973613755</v>
       </c>
     </row>
     <row r="111">
@@ -18338,7 +18338,7 @@
         <v>0.1077065755133246</v>
       </c>
       <c r="R111" t="n">
-        <v>0.1085019970264213</v>
+        <v>0.1085019970263058</v>
       </c>
     </row>
     <row r="113">
@@ -18495,7 +18495,7 @@
         <v>0.9838484637363304</v>
       </c>
       <c r="R115" t="n">
-        <v>0.9904985017512932</v>
+        <v>0.9904985017509822</v>
       </c>
     </row>
     <row r="116">
@@ -18553,7 +18553,7 @@
         <v>0.8399842726228657</v>
       </c>
       <c r="R116" t="n">
-        <v>0.8453992634731889</v>
+        <v>0.8453992634731893</v>
       </c>
     </row>
     <row r="117">
@@ -18611,7 +18611,7 @@
         <v>1.141156614263146</v>
       </c>
       <c r="R117" t="n">
-        <v>1.149827551377732</v>
+        <v>1.149827551377731</v>
       </c>
     </row>
     <row r="118">
@@ -18669,7 +18669,7 @@
         <v>0.1573081505268158</v>
       </c>
       <c r="R118" t="n">
-        <v>0.1593290496264391</v>
+        <v>0.1593290496267488</v>
       </c>
     </row>
     <row r="119">
@@ -18727,7 +18727,7 @@
         <v>0.1438641911134647</v>
       </c>
       <c r="R119" t="n">
-        <v>0.1450992382781042</v>
+        <v>0.1450992382777929</v>
       </c>
     </row>
     <row r="121">
@@ -18884,7 +18884,7 @@
         <v>0.8479044727645937</v>
       </c>
       <c r="R123" t="n">
-        <v>0.8535637685331525</v>
+        <v>0.8535637685331526</v>
       </c>
     </row>
     <row r="124">
@@ -18942,7 +18942,7 @@
         <v>0.6738757595934318</v>
       </c>
       <c r="R124" t="n">
-        <v>0.6795239616463095</v>
+        <v>0.6795239616463093</v>
       </c>
     </row>
     <row r="125">
@@ -19058,7 +19058,7 @@
         <v>0.2106647605260339</v>
       </c>
       <c r="R126" t="n">
-        <v>0.2136825963662734</v>
+        <v>0.2136825963662731</v>
       </c>
     </row>
     <row r="127">
@@ -19116,7 +19116,7 @@
         <v>0.1740287131711619</v>
       </c>
       <c r="R127" t="n">
-        <v>0.1740398068868431</v>
+        <v>0.1740398068868433</v>
       </c>
     </row>
   </sheetData>
@@ -19345,7 +19345,7 @@
         <v>1.002882718792737</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9594036942914492</v>
+        <v>0.959403694291868</v>
       </c>
     </row>
     <row r="5">
@@ -19403,7 +19403,7 @@
         <v>1.358469858860157</v>
       </c>
       <c r="R5" t="n">
-        <v>1.292919093976085</v>
+        <v>1.29291909397608</v>
       </c>
     </row>
     <row r="6">
@@ -19461,7 +19461,7 @@
         <v>0.1961003240356383</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1809501823812996</v>
+        <v>0.1809501823812949</v>
       </c>
     </row>
     <row r="7">
@@ -19519,7 +19519,7 @@
         <v>0.1594868160317815</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1525652173033363</v>
+        <v>0.1525652173029175</v>
       </c>
     </row>
     <row r="9">
@@ -19676,7 +19676,7 @@
         <v>0.9889884213559702</v>
       </c>
       <c r="R11" t="n">
-        <v>0.948374891703705</v>
+        <v>0.9483748917037071</v>
       </c>
     </row>
     <row r="12">
@@ -19734,7 +19734,7 @@
         <v>0.881755222156586</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8473458208921355</v>
+        <v>0.8473458208921295</v>
       </c>
     </row>
     <row r="13">
@@ -19850,7 +19850,7 @@
         <v>0.1392990476692041</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1348996180414493</v>
+        <v>0.134899618041447</v>
       </c>
     </row>
     <row r="15">
@@ -19908,7 +19908,7 @@
         <v>0.1072331991993842</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1010290708115695</v>
+        <v>0.1010290708115776</v>
       </c>
     </row>
     <row r="17">
@@ -20065,7 +20065,7 @@
         <v>0.960640977144387</v>
       </c>
       <c r="R19" t="n">
-        <v>0.948492905960577</v>
+        <v>0.9484929059605788</v>
       </c>
     </row>
     <row r="20">
@@ -20123,7 +20123,7 @@
         <v>0.8375625448789695</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8295947003115527</v>
+        <v>0.8295947003115509</v>
       </c>
     </row>
     <row r="21">
@@ -20239,7 +20239,7 @@
         <v>0.1420951482661287</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1417174569908165</v>
+        <v>0.1417174569908147</v>
       </c>
     </row>
     <row r="23">
@@ -20297,7 +20297,7 @@
         <v>0.1230784322654175</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1188982056490243</v>
+        <v>0.1188982056490279</v>
       </c>
     </row>
     <row r="25">
@@ -20512,7 +20512,7 @@
         <v>0.989462564467388</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9299810048525248</v>
+        <v>0.9299810048525172</v>
       </c>
     </row>
     <row r="29">
@@ -20570,7 +20570,7 @@
         <v>1.28752386533175</v>
       </c>
       <c r="R29" t="n">
-        <v>1.216061780094582</v>
+        <v>1.216061780094595</v>
       </c>
     </row>
     <row r="30">
@@ -20628,7 +20628,7 @@
         <v>0.162155839906136</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1558629886306737</v>
+        <v>0.1558629886306864</v>
       </c>
     </row>
     <row r="31">
@@ -20686,7 +20686,7 @@
         <v>0.1359054609582262</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1302177866113838</v>
+        <v>0.1302177866113916</v>
       </c>
     </row>
     <row r="33">
@@ -20843,7 +20843,7 @@
         <v>0.9789311504868508</v>
       </c>
       <c r="R35" t="n">
-        <v>0.949806266800634</v>
+        <v>0.9498062668006404</v>
       </c>
     </row>
     <row r="36">
@@ -20901,7 +20901,7 @@
         <v>0.8182882353079042</v>
       </c>
       <c r="R36" t="n">
-        <v>0.7922667037042385</v>
+        <v>0.7922667037034161</v>
       </c>
     </row>
     <row r="37">
@@ -21017,7 +21017,7 @@
         <v>0.1779351466181098</v>
       </c>
       <c r="R38" t="n">
-        <v>0.1722160160197423</v>
+        <v>0.1722160160197359</v>
       </c>
     </row>
     <row r="39">
@@ -21075,7 +21075,7 @@
         <v>0.1606429151789466</v>
       </c>
       <c r="R39" t="n">
-        <v>0.1575395630963955</v>
+        <v>0.1575395630972243</v>
       </c>
     </row>
     <row r="41">
@@ -21232,7 +21232,7 @@
         <v>0.8541038132832648</v>
       </c>
       <c r="R43" t="n">
-        <v>0.8172958602643987</v>
+        <v>0.8172958602643989</v>
       </c>
     </row>
     <row r="44">
@@ -21290,7 +21290,7 @@
         <v>0.7139860897367306</v>
       </c>
       <c r="R44" t="n">
-        <v>0.6847580767638846</v>
+        <v>0.6847580767634663</v>
       </c>
     </row>
     <row r="45">
@@ -21348,7 +21348,7 @@
         <v>1.02356716789675</v>
       </c>
       <c r="R45" t="n">
-        <v>0.9755044630865072</v>
+        <v>0.975504463086418</v>
       </c>
     </row>
     <row r="46">
@@ -21406,7 +21406,7 @@
         <v>0.1694633546134856</v>
       </c>
       <c r="R46" t="n">
-        <v>0.1582086028221085</v>
+        <v>0.1582086028220191</v>
       </c>
     </row>
     <row r="47">
@@ -21464,7 +21464,7 @@
         <v>0.1401177235465342</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1325377835005142</v>
+        <v>0.1325377835009326</v>
       </c>
     </row>
     <row r="49">
@@ -21621,7 +21621,7 @@
         <v>0.9382795821512068</v>
       </c>
       <c r="R51" t="n">
-        <v>0.8852083439296666</v>
+        <v>0.8852083439296903</v>
       </c>
     </row>
     <row r="52">
@@ -21679,7 +21679,7 @@
         <v>0.8232389746010318</v>
       </c>
       <c r="R52" t="n">
-        <v>0.7768822252273907</v>
+        <v>0.776882225227385</v>
       </c>
     </row>
     <row r="53">
@@ -21737,7 +21737,7 @@
         <v>1.076151540154844</v>
       </c>
       <c r="R53" t="n">
-        <v>1.014346220487088</v>
+        <v>1.014346220487089</v>
       </c>
     </row>
     <row r="54">
@@ -21795,7 +21795,7 @@
         <v>0.1378719580036377</v>
       </c>
       <c r="R54" t="n">
-        <v>0.129137876557421</v>
+        <v>0.1291378765573983</v>
       </c>
     </row>
     <row r="55">
@@ -21853,7 +21853,7 @@
         <v>0.115040607550175</v>
       </c>
       <c r="R55" t="n">
-        <v>0.1083261187022759</v>
+        <v>0.1083261187023052</v>
       </c>
     </row>
     <row r="57">
@@ -22010,7 +22010,7 @@
         <v>1.058810092994575</v>
       </c>
       <c r="R59" t="n">
-        <v>1.005771528594333</v>
+        <v>1.005771528594328</v>
       </c>
     </row>
     <row r="60">
@@ -22068,7 +22068,7 @@
         <v>0.91557825199123</v>
       </c>
       <c r="R60" t="n">
-        <v>0.8744443622581859</v>
+        <v>0.8744443622581857</v>
       </c>
     </row>
     <row r="61">
@@ -22126,7 +22126,7 @@
         <v>1.210026083533704</v>
       </c>
       <c r="R61" t="n">
-        <v>1.148462569637758</v>
+        <v>1.148462569638034</v>
       </c>
     </row>
     <row r="62">
@@ -22184,7 +22184,7 @@
         <v>0.1512159905391284</v>
       </c>
       <c r="R62" t="n">
-        <v>0.142691041043425</v>
+        <v>0.1426910410437066</v>
       </c>
     </row>
     <row r="63">
@@ -22242,7 +22242,7 @@
         <v>0.1432318410033454</v>
       </c>
       <c r="R63" t="n">
-        <v>0.1313271663361475</v>
+        <v>0.1313271663361422</v>
       </c>
     </row>
     <row r="65">
@@ -22457,7 +22457,7 @@
         <v>0.9390925032898584</v>
       </c>
       <c r="R68" t="n">
-        <v>0.8945263316297262</v>
+        <v>0.8945263316297277</v>
       </c>
     </row>
     <row r="69">
@@ -22631,7 +22631,7 @@
         <v>0.1219423684205169</v>
       </c>
       <c r="R71" t="n">
-        <v>0.119403618311995</v>
+        <v>0.1194036183119934</v>
       </c>
     </row>
     <row r="73">
@@ -22788,7 +22788,7 @@
         <v>0.8667274985109007</v>
       </c>
       <c r="R75" t="n">
-        <v>0.8482050143335518</v>
+        <v>0.8482050143335541</v>
       </c>
     </row>
     <row r="76">
@@ -22846,7 +22846,7 @@
         <v>0.7296283616267274</v>
       </c>
       <c r="R76" t="n">
-        <v>0.7129466847893279</v>
+        <v>0.7129466847888261</v>
       </c>
     </row>
     <row r="77">
@@ -22962,7 +22962,7 @@
         <v>0.1789075789385618</v>
       </c>
       <c r="R78" t="n">
-        <v>0.1819535117469437</v>
+        <v>0.1819535117469414</v>
       </c>
     </row>
     <row r="79">
@@ -23020,7 +23020,7 @@
         <v>0.1370991368841733</v>
       </c>
       <c r="R79" t="n">
-        <v>0.1352583295442239</v>
+        <v>0.1352583295447281</v>
       </c>
     </row>
     <row r="81">
@@ -23177,7 +23177,7 @@
         <v>1.007855598701449</v>
       </c>
       <c r="R83" t="n">
-        <v>0.9901902329761146</v>
+        <v>0.9901902329761432</v>
       </c>
     </row>
     <row r="84">
@@ -23235,7 +23235,7 @@
         <v>0.8958310044978037</v>
       </c>
       <c r="R84" t="n">
-        <v>0.8802255173485629</v>
+        <v>0.8802255173485524</v>
       </c>
     </row>
     <row r="85">
@@ -23351,7 +23351,7 @@
         <v>0.1411270324691465</v>
       </c>
       <c r="R86" t="n">
-        <v>0.1390855172377617</v>
+        <v>0.139085517237733</v>
       </c>
     </row>
     <row r="87">
@@ -23409,7 +23409,7 @@
         <v>0.1120245942036453</v>
       </c>
       <c r="R87" t="n">
-        <v>0.1099647156275517</v>
+        <v>0.1099647156275908</v>
       </c>
     </row>
     <row r="89">
@@ -23624,7 +23624,7 @@
         <v>0.8882297139771033</v>
       </c>
       <c r="R92" t="n">
-        <v>0.7793295130713392</v>
+        <v>0.7793295130713489</v>
       </c>
     </row>
     <row r="93">
@@ -23682,7 +23682,7 @@
         <v>1.091414974116229</v>
       </c>
       <c r="R93" t="n">
-        <v>0.9607397578892511</v>
+        <v>0.9607397578892514</v>
       </c>
     </row>
     <row r="94">
@@ -23740,7 +23740,7 @@
         <v>0.1083766847806401</v>
       </c>
       <c r="R94" t="n">
-        <v>0.09763194820221865</v>
+        <v>0.09763194820221888</v>
       </c>
     </row>
     <row r="95">
@@ -23798,7 +23798,7 @@
         <v>0.09480857535848553</v>
       </c>
       <c r="R95" t="n">
-        <v>0.08377829661569325</v>
+        <v>0.08377829661568359</v>
       </c>
     </row>
     <row r="97">
@@ -23955,7 +23955,7 @@
         <v>1.114607805600352</v>
       </c>
       <c r="R99" t="n">
-        <v>1.073754265746321</v>
+        <v>1.07375426574622</v>
       </c>
     </row>
     <row r="100">
@@ -24013,7 +24013,7 @@
         <v>0.966710560368783</v>
       </c>
       <c r="R100" t="n">
-        <v>0.9244336097567896</v>
+        <v>0.9244336097567892</v>
       </c>
     </row>
     <row r="101">
@@ -24071,7 +24071,7 @@
         <v>1.288640543640795</v>
       </c>
       <c r="R101" t="n">
-        <v>1.239864553899375</v>
+        <v>1.239864553899374</v>
       </c>
     </row>
     <row r="102">
@@ -24129,7 +24129,7 @@
         <v>0.1740327380404434</v>
       </c>
       <c r="R102" t="n">
-        <v>0.1661102881530536</v>
+        <v>0.1661102881531538</v>
       </c>
     </row>
     <row r="103">
@@ -24187,7 +24187,7 @@
         <v>0.1478972452315691</v>
       </c>
       <c r="R103" t="n">
-        <v>0.1493206559895317</v>
+        <v>0.1493206559894312</v>
       </c>
     </row>
     <row r="105">
@@ -24344,7 +24344,7 @@
         <v>0.9619906084016724</v>
       </c>
       <c r="R107" t="n">
-        <v>0.9133347214005716</v>
+        <v>0.9133347214005696</v>
       </c>
     </row>
     <row r="108">
@@ -24402,7 +24402,7 @@
         <v>0.8539701136082881</v>
       </c>
       <c r="R108" t="n">
-        <v>0.8081496103648372</v>
+        <v>0.8081496103648268</v>
       </c>
     </row>
     <row r="109">
@@ -24460,7 +24460,7 @@
         <v>1.080974739082497</v>
       </c>
       <c r="R109" t="n">
-        <v>1.025743217543931</v>
+        <v>1.02574321754404</v>
       </c>
     </row>
     <row r="110">
@@ -24518,7 +24518,7 @@
         <v>0.1189841306808249</v>
       </c>
       <c r="R110" t="n">
-        <v>0.1124084961433598</v>
+        <v>0.1124084961434699</v>
       </c>
     </row>
     <row r="111">
@@ -24576,7 +24576,7 @@
         <v>0.1080204947933843</v>
       </c>
       <c r="R111" t="n">
-        <v>0.1051851110357344</v>
+        <v>0.1051851110357428</v>
       </c>
     </row>
     <row r="113">
@@ -24791,7 +24791,7 @@
         <v>0.8411106133192063</v>
       </c>
       <c r="R116" t="n">
-        <v>0.7777431879406683</v>
+        <v>0.7777431879404223</v>
       </c>
     </row>
     <row r="117">
@@ -24965,7 +24965,7 @@
         <v>0.1439264783860457</v>
       </c>
       <c r="R119" t="n">
-        <v>0.1304750467147044</v>
+        <v>0.1304750467149505</v>
       </c>
     </row>
     <row r="121">
@@ -25122,7 +25122,7 @@
         <v>0.8482335440896369</v>
       </c>
       <c r="R123" t="n">
-        <v>0.8267531515873361</v>
+        <v>0.8267531515873368</v>
       </c>
     </row>
     <row r="124">
@@ -25180,7 +25180,7 @@
         <v>0.6740168434114966</v>
       </c>
       <c r="R124" t="n">
-        <v>0.6565569746263654</v>
+        <v>0.6565569746263659</v>
       </c>
     </row>
     <row r="125">
@@ -25238,7 +25238,7 @@
         <v>1.058851838573404</v>
       </c>
       <c r="R125" t="n">
-        <v>1.030748619540656</v>
+        <v>1.030748619540206</v>
       </c>
     </row>
     <row r="126">
@@ -25296,7 +25296,7 @@
         <v>0.2106182944837669</v>
       </c>
       <c r="R126" t="n">
-        <v>0.20399546795332</v>
+        <v>0.2039954679528695</v>
       </c>
     </row>
     <row r="127">
@@ -25354,7 +25354,7 @@
         <v>0.1742167006781403</v>
       </c>
       <c r="R127" t="n">
-        <v>0.1701961769609707</v>
+        <v>0.1701961769609709</v>
       </c>
     </row>
   </sheetData>
